--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/user-controller/listAdmins-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/user-controller/listAdmins-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="81">
-  <si>
-    <t>Statement: user-controller.listAdmins(options?) – Server Action. No input validation. Delegates to userService.listAdmins(). Returns ActionResult&lt;PageResult&lt;AdminWithUser&gt;&gt;.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="86">
+  <si>
+    <t>Statement: listAdmins(options?) – Accepts optional pagination and search options and returns an ActionResult&lt;Page&lt;MemberWithUser&gt;&gt; containing the matching admins. Returns success with the paginated admin list on success, with items ordered by fullName. Returns success with an empty items array when no admins exist. Returns a failure with an error message when the operation cannot be completed.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: AdminListOptions? { search?, page?, pageSize? }</t>
+    <t>Input: options?: AdminListOptions { page?: number, pageSize?: number, search?: string }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>userService.listAdmins is mock-injected</t>
+    <t>The admin store may be empty or populated. Default pagination applies when options are undefined or partially omitted.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;PageResult&lt;AdminWithUser&gt;&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;Page&lt;MemberWithUser&gt;&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>On success: page returned. On AppError: failure. On error: generic failure.</t>
+    <t>On success: list retrieved successfully, returned page reflects the requested options. On failure: operation fails with an error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,34 +64,25 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>no options</t>
-  </si>
-  <si>
-    <t>service resolves page</t>
-  </si>
-  <si>
-    <t>with filter</t>
-  </si>
-  <si>
-    <t>filter passed to service</t>
-  </si>
-  <si>
-    <t>with pagination</t>
-  </si>
-  <si>
-    <t>pagination passed through</t>
-  </si>
-  <si>
-    <t>service outcome</t>
-  </si>
-  <si>
-    <t>resolves page</t>
-  </si>
-  <si>
-    <t>throws AppError → failure</t>
-  </si>
-  <si>
-    <t>throws Error → generic failure</t>
+    <t>Database state</t>
+  </si>
+  <si>
+    <t>Multiple admins exist, no options → list retrieved successfully, items returned in order by fullName</t>
+  </si>
+  <si>
+    <t>No admins exist, no options → list retrieved successfully, returned items array is empty</t>
+  </si>
+  <si>
+    <t>Search option</t>
+  </si>
+  <si>
+    <t>Search term provided (search: "Admin") → list retrieved successfully, returned items match the search term</t>
+  </si>
+  <si>
+    <t>Service error</t>
+  </si>
+  <si>
+    <t>Operation fails internally → operation fails with the returned error message</t>
   </si>
   <si>
     <t>No TC</t>
@@ -109,49 +100,43 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1,4</t>
-  </si>
-  <si>
-    <t>no options, service resolves { items:[MOCK_ADMIN], total:1 }</t>
-  </si>
-  <si>
-    <t>{ success: true, data.total: 1 }</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>{ search: "Admin" }, service resolves</t>
-  </si>
-  <si>
-    <t>{ success: true }; listAdmins({ search:"Admin" }) called</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>{ page: 2, pageSize: 5 }, service resolves</t>
-  </si>
-  <si>
-    <t>{ success: true }; listAdmins(options) called</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>no options, service throws AppError("Service error")</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Service error" }</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>no options, service throws Error("DB error")</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>no options, two admins exist ordered by fullName ("A Admin", "B Admin")</t>
+  </si>
+  <si>
+    <t>list retrieved successfully, first item fullName is "A Admin", second is "B Admin"</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>no options, no admins exist in the store</t>
+  </si>
+  <si>
+    <t>list retrieved successfully, returned items array is empty</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>options: { search: "Admin" }, matching admins exist</t>
+  </si>
+  <si>
+    <t>list retrieved successfully</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>no options, operation fails internally</t>
+  </si>
+  <si>
+    <t>operation fails with the returned error message</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -160,64 +145,97 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>No numerical boundaries</t>
+    <t>pageSize boundary</t>
+  </si>
+  <si>
+    <t>pageSize: 1 (minimum non-zero): exactly 1 item returned → list retrieved successfully with 1 item</t>
+  </si>
+  <si>
+    <t>pageSize: 0 (zero): no items returned → list retrieved successfully with empty items array</t>
+  </si>
+  <si>
+    <t>search boundary</t>
+  </si>
+  <si>
+    <t>search: "" (empty string): treated as no filter → list retrieved successfully with all items</t>
+  </si>
+  <si>
+    <t>search: "A" (one character): minimum non-empty search term → list retrieved successfully</t>
+  </si>
+  <si>
+    <t>page boundary</t>
+  </si>
+  <si>
+    <t>page: 0 (zero-indexed first page): first page returned → list retrieved successfully</t>
+  </si>
+  <si>
+    <t>page: 1 (one-indexed first page): first page returned → list retrieved successfully</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
+    <t>BVA-1 (pageSize=1)</t>
+  </si>
+  <si>
+    <t>options: { pageSize: 1 }, 5 admins exist</t>
+  </si>
+  <si>
+    <t>list retrieved successfully, returned items array has length 1</t>
+  </si>
+  <si>
+    <t>BVA-2 (pageSize=0)</t>
+  </si>
+  <si>
+    <t>options: { pageSize: 0 }, 5 admins exist</t>
+  </si>
+  <si>
+    <t>BVA-3 (search="")</t>
+  </si>
+  <si>
+    <t>options: { search: "" }, admins exist</t>
+  </si>
+  <si>
+    <t>BVA-4 (search="A")</t>
+  </si>
+  <si>
+    <t>options: { search: "A" }, admins matching "A" exist</t>
+  </si>
+  <si>
+    <t>BVA-5 (page=0)</t>
+  </si>
+  <si>
+    <t>options: { page: 0 }, admins exist</t>
+  </si>
+  <si>
+    <t>BVA-6 (page=1)</t>
+  </si>
+  <si>
+    <t>options: { page: 1 }, admins exist</t>
+  </si>
+  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>No options, service resolves</t>
-  </si>
-  <si>
-    <t>success=true, page returned</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>With search filter</t>
-  </si>
-  <si>
-    <t>success=true, listAdmins(filter) called</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>With pagination</t>
-  </si>
-  <si>
-    <t>success=true, listAdmins(pagination) called</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>Service throws AppError</t>
-  </si>
-  <si>
-    <t>success=false, message from error</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, message="An unexpected error occurred"</t>
+    <t>BVA-1</t>
+  </si>
+  <si>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
   </si>
   <si>
     <t>Testing</t>
@@ -250,16 +268,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-06</t>
+    <t>CTRL-09</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -775,7 +790,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -816,10 +831,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -830,10 +845,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>1</v>
@@ -844,41 +859,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -889,7 +876,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -901,19 +888,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -921,16 +908,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -938,16 +925,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -955,16 +942,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -972,33 +959,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1009,7 +979,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1019,13 +989,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1033,10 +1003,65 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>48</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1047,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1059,19 +1084,121 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1082,7 +1209,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1095,22 +1222,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1118,19 +1245,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1138,19 +1265,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1158,19 +1285,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1178,19 +1305,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1198,19 +1325,119 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>66</v>
+      <c r="E11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1238,16 +1465,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1255,45 +1482,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>77</v>
+      <c r="A3" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="B3" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1302,19 +1529,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>80</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
